--- a/excel_config/indir/z_zhishi_effects.xlsx
+++ b/excel_config/indir/z_zhishi_effects.xlsx
@@ -990,7 +990,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>"cumulative_per_learned_level"</t>
+          <t>cumulative_per_learned_level</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>["add_flat","add_percent"]</t>
+          <t>add_flat:add_percent</t>
         </is>
       </c>
     </row>
